--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-25T10:05:30+00:00</t>
+    <t>2026-03-13T14:11:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T14:11:35+00:00</t>
+    <t>2026-03-13T17:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:00:40+00:00</t>
+    <t>2026-03-13T17:26:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:39+00:00</t>
+    <t>2026-03-13T17:26:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T17:26:16+00:00</t>
+    <t>2026-03-13T22:26:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.1.0-snapsnot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T22:26:12+00:00</t>
+    <t>2026-03-20T08:18:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T08:18:16+00:00</t>
+    <t>2026-03-23T13:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T13:14:10+00:00</t>
+    <t>2026-03-27T09:33:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$82</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3386" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3158" uniqueCount="567">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -444,33 +444,220 @@
     <t>Observation.extension</t>
   </si>
   <si>
+    <t xml:space="preserve">Extension
+</t>
+  </si>
+  <si>
+    <t>Extension</t>
+  </si>
+  <si>
+    <t>An Extension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.extension</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.extension:author</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
+</t>
+  </si>
+  <si>
+    <t>Auteur de l’observation</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.id</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.url</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.extension.extension.value[x]</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>AUT</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode</t>
+  </si>
+  <si>
+    <t>typeCode</t>
+  </si>
+  <si>
+    <t>Type de participation</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:typeCode.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor</t>
+  </si>
+  <si>
+    <t>actor</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.id</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.url</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.extension:actor.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document)
+</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.url</t>
+  </si>
+  <si>
+    <t>Observation.extension.url</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
+  </si>
+  <si>
+    <t>Observation.extension:author.value[x]</t>
+  </si>
+  <si>
+    <t>Observation.extension.value[x]</t>
+  </si>
+  <si>
+    <t>base64Binary
+booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
+  </si>
+  <si>
+    <t>Observation.modifierExtension</t>
+  </si>
+  <si>
     <t>extensions
 user content</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension
-</t>
-  </si>
-  <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>DomainResource.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
-  </si>
-  <si>
-    <t>Observation.modifierExtension</t>
-  </si>
-  <si>
     <t>Extensions that cannot be ignored</t>
   </si>
   <si>
@@ -478,6 +665,9 @@
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
     <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
   </si>
   <si>
@@ -588,9 +778,6 @@
     <t>final</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>Codes providing the status of an observation.</t>
   </si>
   <si>
@@ -613,10 +800,6 @@
   </si>
   <si>
     <t>Observation.category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
   </si>
   <si>
     <t>Classification of  type of observation</t>
@@ -692,39 +875,13 @@
     <t>Observation.code.id</t>
   </si>
   <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Observation.code.extension</t>
   </si>
   <si>
+    <t>Additional content defined by implementations</t>
+  </si>
+  <si>
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
   </si>
   <si>
     <t>Observation.code.coding</t>
@@ -1070,10 +1227,6 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:extension.url}
-</t>
-  </si>
-  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1084,248 +1237,6 @@
   </si>
   <si>
     <t>FiveWs.actor</t>
-  </si>
-  <si>
-    <t>Observation.performer.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author</t>
-  </si>
-  <si>
-    <t>author</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension}
-</t>
-  </si>
-  <si>
-    <t>Auteur de l’observation</t>
-  </si>
-  <si>
-    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.extension.value[x]</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>AUT</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-vs-actor-type-document</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode</t>
-  </si>
-  <si>
-    <t>typeCode</t>
-  </si>
-  <si>
-    <t>Type de participation</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:typeCode.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor</t>
-  </si>
-  <si>
-    <t>actor</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.id</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.extension:actor.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-practitionerRole-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-organization-document|https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-patient-ins-document)
-</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.url</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.url</t>
-  </si>
-  <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-actor-extension</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension:author.value[x]</t>
-  </si>
-  <si>
-    <t>Observation.performer.extension.value[x]</t>
-  </si>
-  <si>
-    <t>base64Binary
-booleancanonicalcodedatedateTimedecimalidinstantintegermarkdownoidpositiveIntstringtimeunsignedInturiurluuidAddressAgeAnnotationAttachmentCodeableConceptCodingContactPointCountDistanceDurationHumanNameIdentifierMoneyPeriodQuantityRangeRatioReferenceSampledDataSignatureTimingContactDetailContributorDataRequirementExpressionParameterDefinitionRelatedArtifactTriggerDefinitionUsageContextDosageMeta</t>
-  </si>
-  <si>
-    <t>Observation.performer.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
-  </si>
-  <si>
-    <t>Reference.reference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ref-1
-</t>
-  </si>
-  <si>
-    <t>Observation.performer.type</t>
-  </si>
-  <si>
-    <t>Type the reference refers to (e.g. "Patient")</t>
-  </si>
-  <si>
-    <t>The expected type of the target of the reference. If both Reference.type and Reference.reference are populated and Reference.reference is a FHIR URL, both SHALL be consistent.
-The type is the Canonical URL of Resource Definition that is the type this reference refers to. References are URLs that are relative to http://hl7.org/fhir/StructureDefinition/ e.g. "Patient" is a reference to http://hl7.org/fhir/StructureDefinition/Patient. Absolute URLs are only allowed for logical models (and can only be used in references in logical models, not resources).</t>
-  </si>
-  <si>
-    <t>This element is used to indicate the type of  the target of the reference. This may be used which ever of the other elements are populated (or not). In some cases, the type of the target may be determined by inspection of the reference (e.g. a RESTful URL) or by resolving the target of the reference; if both the type and a reference is provided, the reference SHALL resolve to a resource of the same type as that specified.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>Aa resource (or, for logical models, the URI of the logical model).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
-  </si>
-  <si>
-    <t>Reference.type</t>
-  </si>
-  <si>
-    <t>Observation.performer.identifier</t>
-  </si>
-  <si>
-    <t>Logical reference, when literal reference is not known</t>
-  </si>
-  <si>
-    <t>An identifier for the target resource. This is used when there is no way to reference the other resource directly, either because the entity it represents is not available through a FHIR server, or because there is no way for the author of the resource to convert a known identifier to an actual location. There is no requirement that a Reference.identifier point to something that is actually exposed as a FHIR instance, but it SHALL point to a business concept that would be expected to be exposed as a FHIR instance, and that instance would need to be of a FHIR resource type allowed by the reference.</t>
-  </si>
-  <si>
-    <t>When an identifier is provided in place of a reference, any system processing the reference will only be able to resolve the identifier to a reference if it understands the business context in which the identifier is used. Sometimes this is global (e.g. a national identifier) but often it is not. For this reason, none of the useful mechanisms described for working with references (e.g. chaining, includes) are possible, nor should servers be expected to be able resolve the reference. Servers may accept an identifier based reference untouched, resolve it, and/or reject it - see CapabilityStatement.rest.resource.referencePolicy. 
-When both an identifier and a literal reference are provided, the literal reference is preferred. Applications processing the resource are allowed - but not required - to check that the identifier matches the literal reference
-Applications converting a logical reference to a literal reference may choose to leave the logical reference present, or remove it.
-Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
-  </si>
-  <si>
-    <t>Reference.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>Observation.performer.display</t>
-  </si>
-  <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
-  </si>
-  <si>
-    <t>Reference.display</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1376,6 +1287,9 @@
   </si>
   <si>
     <t>For many results it is necessary to handle exceptional values in measurements.</t>
+  </si>
+  <si>
+    <t>extensible</t>
   </si>
   <si>
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
@@ -2184,11 +2098,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP88"/>
+  <dimension ref="A1:AP82"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="57.22265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="43.44921875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="48.80859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -3205,7 +3119,7 @@
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -3224,17 +3138,15 @@
         <v>82</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="L9" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="L9" t="s" s="2">
+      <c r="M9" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M9" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="N9" s="2"/>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
         <v>82</v>
@@ -3271,16 +3183,14 @@
         <v>82</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF9" t="s" s="2">
         <v>143</v>
@@ -3307,7 +3217,7 @@
         <v>82</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>82</v>
@@ -3321,11 +3231,13 @@
         <v>145</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="C10" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="D10" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
@@ -3338,26 +3250,22 @@
         <v>82</v>
       </c>
       <c r="I10" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O10" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>82</v>
       </c>
@@ -3405,7 +3313,7 @@
         <v>82</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -3414,7 +3322,7 @@
         <v>81</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>144</v>
@@ -3429,7 +3337,7 @@
         <v>82</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>82</v>
@@ -3438,12 +3346,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3451,33 +3359,31 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N11" s="2"/>
-      <c r="O11" t="s" s="2">
-        <v>154</v>
-      </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>82</v>
       </c>
@@ -3525,34 +3431,34 @@
         <v>82</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="AL11" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>156</v>
+        <v>82</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>157</v>
       </c>
       <c r="AO11" t="s" s="2">
-        <v>158</v>
+        <v>82</v>
       </c>
       <c r="AP11" t="s" s="2">
         <v>82</v>
@@ -3560,18 +3466,18 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>159</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>160</v>
+        <v>82</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>80</v>
+        <v>160</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>81</v>
@@ -3583,21 +3489,19 @@
         <v>82</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>161</v>
+        <v>138</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>162</v>
+        <v>139</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>164</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>82</v>
       </c>
@@ -3633,19 +3537,19 @@
         <v>82</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -3657,19 +3561,19 @@
         <v>82</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="AL12" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>166</v>
+        <v>82</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>167</v>
+        <v>82</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>82</v>
@@ -3680,21 +3584,23 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="C13" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="C13" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="D13" t="s" s="2">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>82</v>
@@ -3703,20 +3609,18 @@
         <v>82</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>173</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>82</v>
@@ -3765,7 +3669,7 @@
         <v>82</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -3777,19 +3681,19 @@
         <v>82</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>174</v>
+        <v>82</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>175</v>
+        <v>82</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>176</v>
+        <v>82</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>82</v>
@@ -3798,12 +3702,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3811,35 +3715,31 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>181</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>82</v>
       </c>
@@ -3848,7 +3748,7 @@
         <v>82</v>
       </c>
       <c r="S14" t="s" s="2">
-        <v>182</v>
+        <v>82</v>
       </c>
       <c r="T14" t="s" s="2">
         <v>82</v>
@@ -3863,13 +3763,13 @@
         <v>82</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>183</v>
+        <v>82</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>185</v>
+        <v>82</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>82</v>
@@ -3887,10 +3787,10 @@
         <v>82</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>156</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>93</v>
@@ -3899,22 +3799,22 @@
         <v>82</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>186</v>
+        <v>82</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>187</v>
+        <v>82</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>189</v>
+        <v>157</v>
       </c>
       <c r="AO14" t="s" s="2">
-        <v>190</v>
+        <v>82</v>
       </c>
       <c r="AP14" t="s" s="2">
         <v>82</v>
@@ -3922,10 +3822,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>191</v>
+        <v>168</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3936,7 +3836,7 @@
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>82</v>
@@ -3948,20 +3848,16 @@
         <v>82</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>193</v>
+        <v>139</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>196</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>82</v>
       </c>
@@ -3985,31 +3881,31 @@
         <v>82</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>197</v>
+        <v>82</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -4021,7 +3917,7 @@
         <v>82</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>82</v>
@@ -4033,25 +3929,25 @@
         <v>82</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>199</v>
+        <v>82</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>200</v>
+        <v>82</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>201</v>
+        <v>169</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>202</v>
+        <v>82</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4061,35 +3957,33 @@
         <v>93</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>192</v>
+        <v>107</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>204</v>
+        <v>172</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>206</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" t="s" s="2">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="S16" t="s" s="2">
         <v>82</v>
@@ -4107,13 +4001,13 @@
         <v>82</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>208</v>
+        <v>82</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>209</v>
+        <v>82</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>82</v>
@@ -4131,7 +4025,7 @@
         <v>82</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>93</v>
@@ -4143,33 +4037,33 @@
         <v>82</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>210</v>
+        <v>82</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>211</v>
+        <v>82</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>213</v>
+        <v>136</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>214</v>
+        <v>82</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>215</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>216</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4192,13 +4086,13 @@
         <v>82</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>218</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>219</v>
+        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4210,7 +4104,7 @@
         <v>82</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>82</v>
+        <v>179</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>82</v>
@@ -4225,13 +4119,11 @@
         <v>82</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>82</v>
+        <v>181</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>82</v>
@@ -4249,7 +4141,7 @@
         <v>82</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>220</v>
+        <v>182</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4261,7 +4153,7 @@
         <v>82</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>82</v>
@@ -4273,7 +4165,7 @@
         <v>82</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>82</v>
@@ -4284,21 +4176,23 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>222</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>184</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>82</v>
@@ -4310,17 +4204,15 @@
         <v>82</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>140</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>82</v>
@@ -4357,19 +4249,19 @@
         <v>82</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>162</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4393,7 +4285,7 @@
         <v>82</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>82</v>
@@ -4404,10 +4296,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>228</v>
+        <v>186</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>228</v>
+        <v>166</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4418,7 +4310,7 @@
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>82</v>
@@ -4427,23 +4319,19 @@
         <v>82</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>229</v>
+        <v>153</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>230</v>
+        <v>154</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>232</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>233</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>82</v>
       </c>
@@ -4491,19 +4379,19 @@
         <v>82</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>82</v>
@@ -4512,10 +4400,10 @@
         <v>82</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>82</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>157</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>82</v>
@@ -4526,10 +4414,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>187</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>168</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4540,7 +4428,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>82</v>
@@ -4552,13 +4440,13 @@
         <v>82</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>218</v>
+        <v>139</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>219</v>
+        <v>140</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4597,31 +4485,31 @@
         <v>82</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>162</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>82</v>
+        <v>144</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>82</v>
@@ -4633,7 +4521,7 @@
         <v>82</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>82</v>
@@ -4644,21 +4532,21 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>238</v>
+        <v>188</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>238</v>
+        <v>170</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
@@ -4670,16 +4558,16 @@
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>139</v>
+        <v>107</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>223</v>
+        <v>172</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4687,7 +4575,7 @@
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" t="s" s="2">
-        <v>82</v>
+        <v>184</v>
       </c>
       <c r="S21" t="s" s="2">
         <v>82</v>
@@ -4717,31 +4605,31 @@
         <v>82</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>227</v>
+        <v>174</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>144</v>
+        <v>82</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>82</v>
@@ -4753,7 +4641,7 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>221</v>
+        <v>136</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -4764,10 +4652,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>239</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>239</v>
+        <v>176</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4787,23 +4675,19 @@
         <v>82</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>240</v>
+        <v>177</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>82</v>
       </c>
@@ -4812,7 +4696,7 @@
         <v>82</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>244</v>
+        <v>82</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>82</v>
@@ -4851,7 +4735,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>245</v>
+        <v>182</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4872,10 +4756,10 @@
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>246</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>247</v>
+        <v>136</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>82</v>
@@ -4886,18 +4770,20 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="C23" s="2"/>
+        <v>159</v>
+      </c>
+      <c r="C23" t="s" s="2">
+        <v>192</v>
+      </c>
       <c r="D23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>93</v>
@@ -4909,20 +4795,18 @@
         <v>82</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>139</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>251</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -4971,19 +4855,19 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>252</v>
+        <v>162</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>82</v>
@@ -4992,10 +4876,10 @@
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>82</v>
@@ -5006,10 +4890,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>255</v>
+        <v>193</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>255</v>
+        <v>166</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5029,21 +4913,19 @@
         <v>82</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>256</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>257</v>
+        <v>155</v>
       </c>
       <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>258</v>
-      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5052,7 +4934,7 @@
         <v>82</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>259</v>
+        <v>82</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>82</v>
@@ -5091,7 +4973,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>156</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5103,7 +4985,7 @@
         <v>82</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>82</v>
@@ -5112,10 +4994,10 @@
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>261</v>
+        <v>82</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>262</v>
+        <v>157</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5126,10 +5008,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>263</v>
+        <v>194</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5140,7 +5022,7 @@
         <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>82</v>
@@ -5149,21 +5031,19 @@
         <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>139</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
+        <v>140</v>
       </c>
       <c r="N25" s="2"/>
-      <c r="O25" t="s" s="2">
-        <v>266</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5172,7 +5052,7 @@
         <v>82</v>
       </c>
       <c r="S25" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="T25" t="s" s="2">
         <v>82</v>
@@ -5199,31 +5079,31 @@
         <v>82</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="AC25" t="s" s="2">
-        <v>82</v>
+        <v>161</v>
       </c>
       <c r="AD25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>268</v>
+        <v>162</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>82</v>
@@ -5232,10 +5112,10 @@
         <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>269</v>
+        <v>82</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>82</v>
@@ -5246,10 +5126,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>271</v>
+        <v>195</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>170</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5257,7 +5137,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>93</v>
@@ -5269,29 +5149,27 @@
         <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>272</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>273</v>
+        <v>171</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>274</v>
+        <v>172</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>82</v>
+        <v>192</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>82</v>
@@ -5333,10 +5211,10 @@
         <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>174</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>93</v>
@@ -5345,7 +5223,7 @@
         <v>82</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>82</v>
@@ -5354,10 +5232,10 @@
         <v>82</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>136</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>82</v>
@@ -5368,10 +5246,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>196</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>280</v>
+        <v>176</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5391,23 +5269,19 @@
         <v>82</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>281</v>
+        <v>177</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5455,7 +5329,7 @@
         <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>285</v>
+        <v>182</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5476,10 +5350,10 @@
         <v>82</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>286</v>
+        <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>287</v>
+        <v>136</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>82</v>
@@ -5488,12 +5362,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>198</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>199</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5507,35 +5381,33 @@
         <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>289</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>290</v>
+        <v>171</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>291</v>
+        <v>172</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>82</v>
+        <v>200</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>82</v>
@@ -5577,10 +5449,10 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>288</v>
+        <v>174</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>93</v>
@@ -5589,22 +5461,22 @@
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>294</v>
+        <v>82</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>295</v>
+        <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>296</v>
+        <v>136</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5612,10 +5484,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>298</v>
+        <v>201</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>298</v>
+        <v>202</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5626,7 +5498,7 @@
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5635,20 +5507,18 @@
         <v>82</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>299</v>
+        <v>203</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>302</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5697,13 +5567,13 @@
         <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>298</v>
+        <v>182</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
@@ -5718,13 +5588,13 @@
         <v>82</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>212</v>
+        <v>82</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>303</v>
+        <v>136</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>297</v>
+        <v>82</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>82</v>
@@ -5732,45 +5602,45 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>304</v>
+        <v>204</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>304</v>
+        <v>204</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>305</v>
+        <v>205</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>306</v>
+        <v>138</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>307</v>
+        <v>206</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>308</v>
+        <v>207</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>309</v>
+        <v>208</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>310</v>
+        <v>209</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
@@ -5819,59 +5689,59 @@
         <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>210</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>311</v>
+        <v>82</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>312</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>313</v>
+        <v>136</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>314</v>
+        <v>82</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>315</v>
+        <v>211</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>315</v>
+        <v>211</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>316</v>
+        <v>82</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
@@ -5880,19 +5750,17 @@
         <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>317</v>
+        <v>212</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>318</v>
+        <v>213</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>320</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>321</v>
+        <v>215</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
@@ -5941,13 +5809,13 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>315</v>
+        <v>211</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
@@ -5956,19 +5824,19 @@
         <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>322</v>
+        <v>216</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>323</v>
+        <v>217</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>324</v>
+        <v>218</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>325</v>
+        <v>219</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>82</v>
@@ -5976,21 +5844,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>326</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>326</v>
+        <v>220</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6002,18 +5870,18 @@
         <v>94</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>327</v>
+        <v>222</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>328</v>
+        <v>223</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>82</v>
       </c>
@@ -6061,13 +5929,13 @@
         <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>326</v>
+        <v>220</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
@@ -6076,19 +5944,19 @@
         <v>105</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>331</v>
+        <v>227</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>332</v>
+        <v>228</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>82</v>
@@ -6096,14 +5964,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>334</v>
+        <v>229</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>334</v>
+        <v>229</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>230</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -6113,7 +5981,7 @@
         <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
@@ -6122,18 +5990,18 @@
         <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>335</v>
+        <v>231</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>336</v>
+        <v>232</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
@@ -6169,17 +6037,19 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="AC33" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>334</v>
+        <v>229</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6194,30 +6064,30 @@
         <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>340</v>
+        <v>235</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>341</v>
+        <v>236</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>342</v>
+        <v>237</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>343</v>
+        <v>82</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>344</v>
+        <v>238</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>344</v>
+        <v>238</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6225,31 +6095,35 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>218</v>
+        <v>239</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>242</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
@@ -6258,7 +6132,7 @@
         <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>82</v>
+        <v>243</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>82</v>
@@ -6273,13 +6147,13 @@
         <v>82</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>82</v>
+        <v>180</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>82</v>
+        <v>244</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>82</v>
+        <v>245</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>82</v>
@@ -6297,10 +6171,10 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>93</v>
@@ -6309,22 +6183,22 @@
         <v>82</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>82</v>
+        <v>246</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>82</v>
+        <v>247</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>82</v>
+        <v>250</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>82</v>
@@ -6332,14 +6206,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>345</v>
+        <v>251</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>345</v>
+        <v>251</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6358,18 +6232,20 @@
         <v>82</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>140</v>
+        <v>252</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>223</v>
+        <v>253</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
@@ -6393,31 +6269,31 @@
         <v>82</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6429,7 +6305,7 @@
         <v>82</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>82</v>
@@ -6441,55 +6317,57 @@
         <v>82</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>221</v>
+        <v>258</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>82</v>
+        <v>259</v>
       </c>
       <c r="AP35" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>346</v>
+        <v>260</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>347</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>82</v>
+        <v>261</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>348</v>
+        <v>190</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>349</v>
+        <v>262</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N36" s="2"/>
-      <c r="O36" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
@@ -6513,13 +6391,13 @@
         <v>82</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>82</v>
@@ -6537,45 +6415,45 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>227</v>
+        <v>260</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>82</v>
+        <v>269</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>82</v>
+        <v>272</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>82</v>
+        <v>274</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>275</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>275</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6598,13 +6476,13 @@
         <v>82</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6655,7 +6533,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6679,7 +6557,7 @@
         <v>82</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6690,18 +6568,18 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>276</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
+        <v>276</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>355</v>
+        <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>81</v>
@@ -6716,15 +6594,17 @@
         <v>82</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>277</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -6761,19 +6641,19 @@
         <v>82</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>224</v>
+        <v>141</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>226</v>
+        <v>142</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>227</v>
+        <v>162</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6797,7 +6677,7 @@
         <v>82</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -6808,23 +6688,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>358</v>
+        <v>279</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>82</v>
@@ -6833,19 +6711,23 @@
         <v>82</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>139</v>
+        <v>280</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>356</v>
+        <v>281</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
       </c>
@@ -6893,7 +6775,7 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>227</v>
+        <v>285</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6905,7 +6787,7 @@
         <v>82</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>82</v>
@@ -6914,10 +6796,10 @@
         <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>82</v>
+        <v>287</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>82</v>
@@ -6928,10 +6810,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>360</v>
+        <v>288</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>361</v>
+        <v>288</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6954,13 +6836,13 @@
         <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>219</v>
+        <v>155</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7011,7 +6893,7 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>220</v>
+        <v>156</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7035,7 +6917,7 @@
         <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>221</v>
+        <v>157</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>82</v>
@@ -7046,21 +6928,21 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>362</v>
+        <v>289</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>363</v>
+        <v>289</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7072,15 +6954,17 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>356</v>
+        <v>277</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>208</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7117,19 +7001,19 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>224</v>
+        <v>141</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>225</v>
+        <v>161</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>226</v>
+        <v>142</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>227</v>
+        <v>162</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7153,7 +7037,7 @@
         <v>82</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>82</v>
@@ -7164,10 +7048,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>364</v>
+        <v>290</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>365</v>
+        <v>290</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7175,7 +7059,7 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>93</v>
@@ -7187,30 +7071,32 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
         <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>366</v>
+        <v>291</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>367</v>
+        <v>292</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>293</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" t="s" s="2">
-        <v>359</v>
+        <v>82</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>82</v>
+        <v>295</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>82</v>
@@ -7249,10 +7135,10 @@
         <v>82</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>369</v>
+        <v>296</v>
       </c>
       <c r="AG42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
         <v>93</v>
@@ -7261,7 +7147,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7270,10 +7156,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>136</v>
+        <v>298</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7284,10 +7170,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>370</v>
+        <v>299</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>371</v>
+        <v>299</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7307,18 +7193,20 @@
         <v>82</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>372</v>
+        <v>300</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>302</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7328,7 +7216,7 @@
         <v>82</v>
       </c>
       <c r="S43" t="s" s="2">
-        <v>374</v>
+        <v>82</v>
       </c>
       <c r="T43" t="s" s="2">
         <v>82</v>
@@ -7343,11 +7231,13 @@
         <v>82</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y43" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z43" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>82</v>
@@ -7365,7 +7255,7 @@
         <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>376</v>
+        <v>303</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7386,10 +7276,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>82</v>
+        <v>304</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>136</v>
+        <v>305</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7400,14 +7290,12 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>377</v>
+        <v>306</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>378</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7425,19 +7313,21 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>379</v>
+        <v>307</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>357</v>
+        <v>308</v>
       </c>
       <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7446,7 +7336,7 @@
         <v>82</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>82</v>
+        <v>310</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>82</v>
@@ -7485,19 +7375,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>227</v>
+        <v>311</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7506,10 +7396,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7520,10 +7410,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>380</v>
+        <v>314</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>314</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7543,19 +7433,21 @@
         <v>82</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>218</v>
+        <v>315</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>219</v>
+        <v>316</v>
       </c>
       <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
+      <c r="O45" t="s" s="2">
+        <v>317</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>82</v>
       </c>
@@ -7564,7 +7456,7 @@
         <v>82</v>
       </c>
       <c r="S45" t="s" s="2">
-        <v>82</v>
+        <v>318</v>
       </c>
       <c r="T45" t="s" s="2">
         <v>82</v>
@@ -7603,7 +7495,7 @@
         <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>220</v>
+        <v>319</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7615,7 +7507,7 @@
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7624,10 +7516,10 @@
         <v>82</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>82</v>
+        <v>320</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>221</v>
+        <v>321</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>82</v>
@@ -7638,10 +7530,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>381</v>
+        <v>322</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>363</v>
+        <v>322</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7652,7 +7544,7 @@
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7661,19 +7553,23 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>139</v>
+        <v>323</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>356</v>
+        <v>324</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
@@ -7709,31 +7605,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>227</v>
+        <v>328</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -7742,10 +7638,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>329</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>82</v>
+        <v>330</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -7756,10 +7652,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>382</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>365</v>
+        <v>331</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7767,7 +7663,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -7779,27 +7675,29 @@
         <v>82</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>153</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>366</v>
+        <v>332</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>367</v>
+        <v>333</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>378</v>
+        <v>82</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -7841,10 +7739,10 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>369</v>
+        <v>336</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>93</v>
@@ -7853,7 +7751,7 @@
         <v>82</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>82</v>
@@ -7862,10 +7760,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>82</v>
+        <v>337</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>136</v>
+        <v>338</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -7874,12 +7772,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="48" hidden="true">
+    <row r="48">
       <c r="A48" t="s" s="2">
-        <v>383</v>
+        <v>339</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>371</v>
+        <v>339</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7887,31 +7785,35 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>192</v>
+        <v>340</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>372</v>
+        <v>341</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
@@ -7959,7 +7861,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>376</v>
+        <v>339</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7974,19 +7876,19 @@
         <v>105</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>136</v>
+        <v>347</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>82</v>
@@ -7994,23 +7896,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>384</v>
+        <v>349</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>82</v>
@@ -8019,18 +7919,20 @@
         <v>82</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>139</v>
+        <v>350</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>352</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>353</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>82</v>
@@ -8079,7 +7981,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>227</v>
+        <v>349</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8091,7 +7993,7 @@
         <v>82</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>82</v>
@@ -8100,13 +8002,13 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>82</v>
+        <v>271</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>82</v>
@@ -8114,14 +8016,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>355</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8137,19 +8039,23 @@
         <v>82</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>217</v>
+        <v>357</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>218</v>
+        <v>358</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>361</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
       </c>
@@ -8197,7 +8103,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>220</v>
+        <v>355</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8209,65 +8115,69 @@
         <v>82</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>82</v>
+        <v>363</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>221</v>
+        <v>364</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="51" hidden="true">
+    <row r="51">
       <c r="A51" t="s" s="2">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>82</v>
+        <v>367</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>139</v>
+        <v>368</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>356</v>
+        <v>369</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="N51" s="2"/>
-      <c r="O51" s="2"/>
+        <v>370</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>372</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
       </c>
@@ -8303,46 +8213,46 @@
         <v>82</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>225</v>
+        <v>82</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>227</v>
+        <v>366</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>82</v>
+        <v>373</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>82</v>
+        <v>374</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>82</v>
+        <v>376</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>82</v>
@@ -8350,10 +8260,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8361,7 +8271,7 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
@@ -8373,19 +8283,19 @@
         <v>82</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>378</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>366</v>
+        <v>379</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8393,7 +8303,7 @@
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>82</v>
@@ -8435,10 +8345,10 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="AG52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH52" t="s" s="2">
         <v>93</v>
@@ -8447,7 +8357,7 @@
         <v>82</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>82</v>
@@ -8456,13 +8366,13 @@
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>136</v>
+        <v>383</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>384</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
@@ -8470,10 +8380,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>371</v>
+        <v>385</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8484,7 +8394,7 @@
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>82</v>
@@ -8493,19 +8403,21 @@
         <v>82</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+      <c r="O53" t="s" s="2">
+        <v>389</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8553,13 +8465,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8568,30 +8480,30 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>82</v>
+        <v>390</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>82</v>
+        <v>391</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>136</v>
+        <v>392</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8605,33 +8517,35 @@
         <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>107</v>
+        <v>190</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>366</v>
+        <v>395</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>367</v>
+        <v>396</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>82</v>
@@ -8649,13 +8563,11 @@
         <v>82</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="Y54" s="2"/>
       <c r="Z54" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>82</v>
@@ -8673,45 +8585,45 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="AG54" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>82</v>
+        <v>400</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>82</v>
+        <v>402</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>136</v>
+        <v>403</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8722,7 +8634,7 @@
         <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>82</v>
@@ -8734,16 +8646,20 @@
         <v>82</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>396</v>
+        <v>190</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+        <v>407</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="O55" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
       </c>
@@ -8767,13 +8683,13 @@
         <v>82</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>82</v>
@@ -8791,7 +8707,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>376</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8800,7 +8716,7 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>105</v>
@@ -8812,10 +8728,10 @@
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>82</v>
+        <v>136</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>136</v>
+        <v>414</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>82</v>
@@ -8824,16 +8740,16 @@
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>397</v>
+        <v>415</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8843,27 +8759,29 @@
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>398</v>
+        <v>417</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>399</v>
+        <v>418</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -8887,13 +8805,11 @@
         <v>82</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>82</v>
+        <v>421</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>82</v>
@@ -8911,16 +8827,16 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>401</v>
+        <v>415</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>402</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>105</v>
@@ -8929,27 +8845,27 @@
         <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>136</v>
+        <v>424</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>403</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8960,30 +8876,32 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>107</v>
+        <v>427</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>405</v>
+        <v>429</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>431</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9007,13 +8925,13 @@
         <v>82</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>408</v>
+        <v>82</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>82</v>
@@ -9031,13 +8949,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>410</v>
+        <v>426</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9052,10 +8970,10 @@
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>136</v>
+        <v>433</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>82</v>
@@ -9064,12 +8982,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9083,25 +9001,25 @@
         <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>151</v>
+        <v>190</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>413</v>
+        <v>436</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9127,13 +9045,13 @@
         <v>82</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>82</v>
@@ -9151,7 +9069,7 @@
         <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>415</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9169,27 +9087,27 @@
         <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9203,27 +9121,29 @@
         <v>93</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="O59" s="2"/>
+        <v>447</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9247,13 +9167,11 @@
         <v>82</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="Y59" s="2"/>
       <c r="Z59" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>82</v>
@@ -9271,7 +9189,7 @@
         <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>444</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9292,10 +9210,10 @@
         <v>82</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>82</v>
+        <v>450</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>136</v>
+        <v>451</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
@@ -9304,12 +9222,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9317,35 +9235,33 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G60" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>192</v>
+        <v>453</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>423</v>
+        <v>454</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>424</v>
+        <v>455</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9369,11 +9285,13 @@
         <v>82</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="Y60" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z60" t="s" s="2">
-        <v>427</v>
+        <v>82</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>82</v>
@@ -9391,7 +9309,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9400,7 +9318,7 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>105</v>
@@ -9409,27 +9327,27 @@
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>429</v>
+        <v>457</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>430</v>
+        <v>458</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>431</v>
+        <v>459</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>432</v>
+        <v>460</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9452,20 +9370,18 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>192</v>
+        <v>462</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>434</v>
+        <v>463</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>435</v>
+        <v>464</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>465</v>
+      </c>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9489,13 +9405,13 @@
         <v>82</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>407</v>
+        <v>82</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>82</v>
@@ -9513,7 +9429,7 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>433</v>
+        <v>461</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9522,7 +9438,7 @@
         <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>105</v>
@@ -9531,41 +9447,41 @@
         <v>82</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>82</v>
+        <v>466</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>136</v>
+        <v>467</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>441</v>
+        <v>468</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
@@ -9574,19 +9490,19 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>192</v>
+        <v>471</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>444</v>
+        <v>472</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>445</v>
+        <v>473</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>446</v>
+        <v>474</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9611,11 +9527,13 @@
         <v>82</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y62" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z62" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>82</v>
@@ -9633,7 +9551,7 @@
         <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>442</v>
+        <v>470</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9645,33 +9563,33 @@
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>105</v>
+        <v>476</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>453</v>
+        <v>479</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9682,10 +9600,10 @@
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I63" t="s" s="2">
         <v>82</v>
@@ -9694,20 +9612,16 @@
         <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>454</v>
+        <v>153</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>455</v>
+        <v>154</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -9755,19 +9669,19 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>453</v>
+        <v>156</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>82</v>
@@ -9776,10 +9690,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>460</v>
+        <v>157</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -9788,26 +9702,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>461</v>
+        <v>480</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>82</v>
@@ -9816,16 +9730,16 @@
         <v>82</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>462</v>
+        <v>277</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>463</v>
+        <v>278</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>464</v>
+        <v>208</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9851,13 +9765,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>465</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>466</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -9875,80 +9789,80 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>461</v>
+        <v>162</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>468</v>
+        <v>82</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>469</v>
+        <v>157</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>470</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>471</v>
+        <v>481</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I65" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="I65" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="J65" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>192</v>
+        <v>138</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>474</v>
+        <v>208</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>475</v>
+        <v>209</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -9973,11 +9887,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y65" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z65" t="s" s="2">
-        <v>476</v>
+        <v>82</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -9995,19 +9911,19 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>82</v>
@@ -10016,10 +9932,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>477</v>
+        <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>478</v>
+        <v>136</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10030,10 +9946,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10056,17 +9972,15 @@
         <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>489</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10115,7 +10029,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10124,7 +10038,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10133,27 +10047,27 @@
         <v>82</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>484</v>
+        <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10176,17 +10090,15 @@
         <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>495</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10235,7 +10147,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10244,7 +10156,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10253,19 +10165,19 @@
         <v>82</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>493</v>
+        <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" hidden="true">
@@ -10284,7 +10196,7 @@
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10296,19 +10208,19 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L68" t="s" s="2">
         <v>498</v>
       </c>
-      <c r="L68" t="s" s="2">
+      <c r="M68" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
@@ -10333,13 +10245,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>82</v>
+        <v>502</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>82</v>
+        <v>503</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10363,25 +10275,25 @@
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>503</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>505</v>
+        <v>424</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10406,7 +10318,7 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10418,16 +10330,20 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>218</v>
+        <v>507</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+        <v>508</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
       </c>
@@ -10451,13 +10367,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10475,31 +10391,31 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>220</v>
+        <v>506</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>82</v>
+        <v>504</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>82</v>
+        <v>505</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>221</v>
+        <v>424</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10510,21 +10426,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>82</v>
@@ -10536,18 +10452,18 @@
         <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>139</v>
+        <v>514</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>140</v>
+        <v>515</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>516</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" t="s" s="2">
+        <v>517</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10595,19 +10511,19 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>227</v>
+        <v>513</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10619,7 +10535,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>221</v>
+        <v>518</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10630,46 +10546,42 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>508</v>
+        <v>519</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>521</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10717,19 +10629,19 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -10738,10 +10650,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>136</v>
+        <v>522</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -10752,10 +10664,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10766,7 +10678,7 @@
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -10775,18 +10687,20 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>526</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>527</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -10835,16 +10749,16 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>105</v>
@@ -10856,10 +10770,10 @@
         <v>82</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>519</v>
+        <v>529</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -10870,10 +10784,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10884,7 +10798,7 @@
         <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -10893,18 +10807,20 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>534</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -10953,16 +10869,16 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>520</v>
+        <v>530</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>517</v>
+        <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>105</v>
@@ -10974,10 +10890,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -10988,10 +10904,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11002,7 +10918,7 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
@@ -11011,22 +10927,22 @@
         <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>192</v>
+        <v>471</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
@@ -11051,13 +10967,13 @@
         <v>82</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>529</v>
+        <v>82</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>82</v>
@@ -11075,13 +10991,13 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>82</v>
@@ -11093,13 +11009,13 @@
         <v>82</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>451</v>
+        <v>542</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11110,10 +11026,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>533</v>
+        <v>543</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11124,7 +11040,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11136,20 +11052,16 @@
         <v>82</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>192</v>
+        <v>153</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>534</v>
+        <v>154</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>537</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11173,13 +11085,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>207</v>
+        <v>82</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>538</v>
+        <v>82</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>539</v>
+        <v>82</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11197,31 +11109,31 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>533</v>
+        <v>156</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>532</v>
+        <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>451</v>
+        <v>157</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11232,21 +11144,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>82</v>
+        <v>205</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>82</v>
@@ -11258,18 +11170,18 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>541</v>
+        <v>138</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>542</v>
+        <v>277</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N76" s="2"/>
-      <c r="O76" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>82</v>
       </c>
@@ -11317,19 +11229,19 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>540</v>
+        <v>162</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>82</v>
@@ -11341,7 +11253,7 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>545</v>
+        <v>157</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11352,42 +11264,46 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>82</v>
+        <v>482</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>217</v>
+        <v>138</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>547</v>
+        <v>483</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
+        <v>484</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>209</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
       </c>
@@ -11435,19 +11351,19 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>546</v>
+        <v>485</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>105</v>
+        <v>144</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>82</v>
@@ -11456,10 +11372,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>518</v>
+        <v>82</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>549</v>
+        <v>136</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11470,10 +11386,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11481,10 +11397,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>82</v>
@@ -11496,18 +11412,20 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>551</v>
+        <v>190</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="O78" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
       </c>
@@ -11531,13 +11449,13 @@
         <v>82</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>82</v>
+        <v>268</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>82</v>
@@ -11555,13 +11473,13 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>82</v>
@@ -11573,16 +11491,16 @@
         <v>82</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>82</v>
+        <v>550</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>555</v>
+        <v>271</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>556</v>
+        <v>272</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="AP78" t="s" s="2">
         <v>82</v>
@@ -11590,10 +11508,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11604,7 +11522,7 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11616,18 +11534,20 @@
         <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>560</v>
+        <v>396</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>554</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11675,13 +11595,13 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
@@ -11693,27 +11613,27 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>82</v>
+        <v>555</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>555</v>
+        <v>402</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>562</v>
+        <v>403</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11724,7 +11644,7 @@
         <v>80</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>82</v>
@@ -11733,22 +11653,22 @@
         <v>82</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>498</v>
+        <v>190</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>564</v>
+        <v>557</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>565</v>
+        <v>558</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>566</v>
+        <v>559</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>567</v>
+        <v>409</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -11773,13 +11693,13 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>82</v>
+        <v>411</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -11797,16 +11717,16 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>82</v>
+        <v>413</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>105</v>
@@ -11818,10 +11738,10 @@
         <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>568</v>
+        <v>136</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>569</v>
+        <v>414</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -11832,21 +11752,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>570</v>
+        <v>560</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>82</v>
+        <v>416</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -11858,16 +11778,20 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>217</v>
+        <v>190</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>218</v>
+        <v>561</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+        <v>418</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>420</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -11891,13 +11815,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>82</v>
+        <v>562</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>82</v>
+        <v>563</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -11915,49 +11839,49 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>220</v>
+        <v>560</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>82</v>
+        <v>422</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>221</v>
+        <v>424</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>82</v>
+        <v>425</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -11976,18 +11900,20 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>140</v>
+        <v>565</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>223</v>
+        <v>566</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>474</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>475</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12035,7 +11961,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>227</v>
+        <v>564</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12047,7 +11973,7 @@
         <v>82</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>82</v>
@@ -12056,752 +11982,20 @@
         <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>82</v>
+        <v>477</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>221</v>
+        <v>478</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="83" hidden="true">
-      <c r="A83" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="B83" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="C83" s="2"/>
-      <c r="D83" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="E83" s="2"/>
-      <c r="F83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I83" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="J83" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K83" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="P83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q83" s="2"/>
-      <c r="R83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF83" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="AG83" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH83" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ83" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="AK83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="84" hidden="true">
-      <c r="A84" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="B84" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="C84" s="2"/>
-      <c r="D84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E84" s="2"/>
-      <c r="F84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="G84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J84" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K84" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L84" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="P84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q84" s="2"/>
-      <c r="R84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X84" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="Y84" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="Z84" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="AA84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF84" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AG84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AH84" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ84" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL84" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AM84" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="B85" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="C85" s="2"/>
-      <c r="D85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E85" s="2"/>
-      <c r="F85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J85" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="K85" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="L85" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="M85" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="P85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q85" s="2"/>
-      <c r="R85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF85" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AG85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH85" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ85" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL85" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="AM85" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="86" hidden="true">
-      <c r="A86" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="B86" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="C86" s="2"/>
-      <c r="D86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E86" s="2"/>
-      <c r="F86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L86" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="M86" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="P86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q86" s="2"/>
-      <c r="R86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X86" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="Y86" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="Z86" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AA86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF86" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="AG86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH86" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI86" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="AJ86" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM86" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="87" hidden="true">
-      <c r="A87" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="B87" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="C87" s="2"/>
-      <c r="D87" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="E87" s="2"/>
-      <c r="F87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="L87" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="M87" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q87" s="2"/>
-      <c r="R87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X87" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="Y87" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="Z87" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="AA87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF87" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AG87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH87" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ87" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL87" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AO87" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP87" t="s" s="2">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="88" hidden="true">
-      <c r="A88" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="C88" s="2"/>
-      <c r="D88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E88" s="2"/>
-      <c r="F88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K88" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="M88" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="P88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q88" s="2"/>
-      <c r="R88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF88" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG88" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH88" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ88" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM88" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP88" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP88">
+  <autoFilter ref="A1:AP82">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12811,7 +12005,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI87">
+  <conditionalFormatting sqref="A2:AI81">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
+++ b/main/ig/StructureDefinition-fr-observation-contra-indications-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
